--- a/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_limpio.xlsx
+++ b/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_limpio.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>Jugador</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>Bryan Zaragoza</t>
+  </si>
+  <si>
+    <t>Mikel Oyarzábal</t>
   </si>
   <si>
     <t>J. Moncayola</t>
@@ -683,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1107,25 +1110,25 @@
         <v>23</v>
       </c>
       <c r="B17">
-        <v>1733</v>
+        <v>1585</v>
       </c>
       <c r="C17">
-        <v>78.5</v>
+        <v>76.2</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1133,25 +1136,25 @@
         <v>24</v>
       </c>
       <c r="B18">
-        <v>1582</v>
+        <v>1733</v>
       </c>
       <c r="C18">
-        <v>80.8</v>
+        <v>78.5</v>
       </c>
       <c r="D18">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H18">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1159,25 +1162,25 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>1532</v>
+        <v>1582</v>
       </c>
       <c r="C19">
-        <v>88.5</v>
+        <v>80.8</v>
       </c>
       <c r="D19">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E19">
-        <v>46.5</v>
+        <v>42.9</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G19">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1185,25 +1188,25 @@
         <v>26</v>
       </c>
       <c r="B20">
-        <v>1880</v>
+        <v>1532</v>
       </c>
       <c r="C20">
-        <v>90.5</v>
+        <v>88.5</v>
       </c>
       <c r="D20">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E20">
-        <v>66.7</v>
+        <v>46.5</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H20">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1211,25 +1214,25 @@
         <v>27</v>
       </c>
       <c r="B21">
-        <v>1091</v>
+        <v>1880</v>
       </c>
       <c r="C21">
-        <v>67.3</v>
+        <v>90.5</v>
       </c>
       <c r="D21">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="E21">
-        <v>53.5</v>
+        <v>66.7</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G21">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H21">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1237,25 +1240,25 @@
         <v>28</v>
       </c>
       <c r="B22">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="C22">
-        <v>81.5</v>
+        <v>67.3</v>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E22">
-        <v>43.8</v>
+        <v>53.5</v>
       </c>
       <c r="F22">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G22">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H22">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1263,25 +1266,25 @@
         <v>29</v>
       </c>
       <c r="B23">
-        <v>1168</v>
+        <v>1063</v>
       </c>
       <c r="C23">
-        <v>76.3</v>
+        <v>81.5</v>
       </c>
       <c r="D23">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="E23">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H23">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1289,25 +1292,25 @@
         <v>30</v>
       </c>
       <c r="B24">
-        <v>1055</v>
+        <v>1168</v>
       </c>
       <c r="C24">
-        <v>85.3</v>
+        <v>76.3</v>
       </c>
       <c r="D24">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="E24">
-        <v>59.4</v>
+        <v>43.3</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H24">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1315,25 +1318,25 @@
         <v>31</v>
       </c>
       <c r="B25">
-        <v>999</v>
+        <v>1055</v>
       </c>
       <c r="C25">
-        <v>75.8</v>
+        <v>85.3</v>
       </c>
       <c r="D25">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E25">
-        <v>41.7</v>
+        <v>59.4</v>
       </c>
       <c r="F25">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1341,25 +1344,25 @@
         <v>32</v>
       </c>
       <c r="B26">
-        <v>1910</v>
+        <v>999</v>
       </c>
       <c r="C26">
-        <v>88.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="D26">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E26">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1367,25 +1370,25 @@
         <v>33</v>
       </c>
       <c r="B27">
-        <v>959</v>
+        <v>1910</v>
       </c>
       <c r="C27">
-        <v>84.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D27">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="E27">
-        <v>43.3</v>
+        <v>44.4</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G27">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H27">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1393,25 +1396,25 @@
         <v>34</v>
       </c>
       <c r="B28">
-        <v>1187</v>
+        <v>959</v>
       </c>
       <c r="C28">
-        <v>83.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="D28">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="E28">
-        <v>59</v>
+        <v>43.3</v>
       </c>
       <c r="F28">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G28">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H28">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1419,25 +1422,25 @@
         <v>35</v>
       </c>
       <c r="B29">
-        <v>1607</v>
+        <v>1187</v>
       </c>
       <c r="C29">
-        <v>82.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D29">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1445,25 +1448,25 @@
         <v>36</v>
       </c>
       <c r="B30">
-        <v>934</v>
+        <v>1607</v>
       </c>
       <c r="C30">
-        <v>78.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D30">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E30">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G30">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1471,25 +1474,25 @@
         <v>37</v>
       </c>
       <c r="B31">
-        <v>1751</v>
+        <v>934</v>
       </c>
       <c r="C31">
-        <v>70.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D31">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="E31">
-        <v>47.5</v>
+        <v>28.6</v>
       </c>
       <c r="F31">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G31">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H31">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1497,25 +1500,25 @@
         <v>38</v>
       </c>
       <c r="B32">
-        <v>1528</v>
+        <v>1751</v>
       </c>
       <c r="C32">
-        <v>88.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="E32">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G32">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H32">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1523,25 +1526,25 @@
         <v>39</v>
       </c>
       <c r="B33">
-        <v>2004</v>
+        <v>1528</v>
       </c>
       <c r="C33">
-        <v>87.2</v>
+        <v>88.2</v>
       </c>
       <c r="D33">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>41.7</v>
+        <v>47.1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1549,19 +1552,19 @@
         <v>40</v>
       </c>
       <c r="B34">
-        <v>819</v>
+        <v>2004</v>
       </c>
       <c r="C34">
-        <v>79.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D34">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>13</v>
@@ -1575,25 +1578,25 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>1416</v>
+        <v>819</v>
       </c>
       <c r="C35">
-        <v>81.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D35">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E35">
-        <v>52.5</v>
+        <v>38.5</v>
       </c>
       <c r="F35">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H35">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1601,25 +1604,25 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>1973</v>
+        <v>1416</v>
       </c>
       <c r="C36">
-        <v>88</v>
+        <v>81.8</v>
       </c>
       <c r="D36">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E36">
-        <v>62.1</v>
+        <v>52.5</v>
       </c>
       <c r="F36">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G36">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H36">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1627,25 +1630,25 @@
         <v>43</v>
       </c>
       <c r="B37">
-        <v>1594</v>
+        <v>1973</v>
       </c>
       <c r="C37">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D37">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E37">
-        <v>56.1</v>
+        <v>62.1</v>
       </c>
       <c r="F37">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>40</v>
+      </c>
+      <c r="H37">
         <v>19</v>
-      </c>
-      <c r="G37">
-        <v>39</v>
-      </c>
-      <c r="H37">
-        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1653,25 +1656,25 @@
         <v>44</v>
       </c>
       <c r="B38">
-        <v>1850</v>
+        <v>1594</v>
       </c>
       <c r="C38">
-        <v>90.3</v>
+        <v>84</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="E38">
-        <v>63.3</v>
+        <v>56.1</v>
       </c>
       <c r="F38">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H38">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1679,25 +1682,25 @@
         <v>45</v>
       </c>
       <c r="B39">
-        <v>1258</v>
+        <v>1850</v>
       </c>
       <c r="C39">
-        <v>74.8</v>
+        <v>90.3</v>
       </c>
       <c r="D39">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>52.9</v>
+        <v>63.3</v>
       </c>
       <c r="F39">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>18</v>
+      </c>
+      <c r="H39">
         <v>19</v>
-      </c>
-      <c r="G39">
-        <v>14</v>
-      </c>
-      <c r="H39">
-        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1705,25 +1708,25 @@
         <v>46</v>
       </c>
       <c r="B40">
-        <v>1212</v>
+        <v>1258</v>
       </c>
       <c r="C40">
-        <v>85.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D40">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="E40">
-        <v>40</v>
+        <v>52.9</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G40">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1731,25 +1734,25 @@
         <v>47</v>
       </c>
       <c r="B41">
-        <v>1427</v>
+        <v>1212</v>
       </c>
       <c r="C41">
-        <v>83.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D41">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G41">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H41">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1757,25 +1760,25 @@
         <v>48</v>
       </c>
       <c r="B42">
-        <v>1584</v>
+        <v>1427</v>
       </c>
       <c r="C42">
-        <v>85.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E42">
-        <v>64</v>
+        <v>33.3</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G42">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H42">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1783,25 +1786,25 @@
         <v>49</v>
       </c>
       <c r="B43">
-        <v>1362</v>
+        <v>1584</v>
       </c>
       <c r="C43">
-        <v>73.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D43">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E43">
-        <v>34.8</v>
+        <v>64</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G43">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H43">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1809,25 +1812,25 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>1129</v>
+        <v>1362</v>
       </c>
       <c r="C44">
-        <v>80.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="D44">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E44">
-        <v>35.5</v>
+        <v>34.8</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G44">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H44">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1835,25 +1838,25 @@
         <v>51</v>
       </c>
       <c r="B45">
-        <v>1331</v>
+        <v>1129</v>
       </c>
       <c r="C45">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E45">
-        <v>56.4</v>
+        <v>35.5</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H45">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1861,25 +1864,25 @@
         <v>52</v>
       </c>
       <c r="B46">
-        <v>1545</v>
+        <v>1331</v>
       </c>
       <c r="C46">
-        <v>85.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D46">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E46">
-        <v>51</v>
+        <v>56.4</v>
       </c>
       <c r="F46">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="G46">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1887,25 +1890,25 @@
         <v>53</v>
       </c>
       <c r="B47">
-        <v>809</v>
+        <v>1545</v>
       </c>
       <c r="C47">
-        <v>83</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D47">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E47">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H47">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1913,22 +1916,22 @@
         <v>54</v>
       </c>
       <c r="B48">
-        <v>930</v>
+        <v>809</v>
       </c>
       <c r="C48">
-        <v>72.5</v>
+        <v>83</v>
       </c>
       <c r="D48">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E48">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F48">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G48">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H48">
         <v>14</v>
@@ -1939,25 +1942,25 @@
         <v>55</v>
       </c>
       <c r="B49">
-        <v>1862</v>
+        <v>930</v>
       </c>
       <c r="C49">
-        <v>82.5</v>
+        <v>72.5</v>
       </c>
       <c r="D49">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E49">
-        <v>57.8</v>
+        <v>35</v>
       </c>
       <c r="F49">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G49">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H49">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1965,25 +1968,25 @@
         <v>56</v>
       </c>
       <c r="B50">
-        <v>1235</v>
+        <v>1862</v>
       </c>
       <c r="C50">
-        <v>77.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D50">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E50">
-        <v>41</v>
+        <v>57.8</v>
       </c>
       <c r="F50">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G50">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H50">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1991,25 +1994,25 @@
         <v>57</v>
       </c>
       <c r="B51">
-        <v>843</v>
+        <v>1235</v>
       </c>
       <c r="C51">
-        <v>88</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D51">
+        <v>92</v>
+      </c>
+      <c r="E51">
+        <v>41</v>
+      </c>
+      <c r="F51">
+        <v>23</v>
+      </c>
+      <c r="G51">
         <v>28</v>
       </c>
-      <c r="E51">
-        <v>60</v>
-      </c>
-      <c r="F51">
-        <v>12</v>
-      </c>
-      <c r="G51">
-        <v>18</v>
-      </c>
       <c r="H51">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2017,25 +2020,25 @@
         <v>58</v>
       </c>
       <c r="B52">
-        <v>1627</v>
+        <v>843</v>
       </c>
       <c r="C52">
-        <v>85.7</v>
+        <v>88</v>
       </c>
       <c r="D52">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E52">
-        <v>44.8</v>
+        <v>60</v>
       </c>
       <c r="F52">
         <v>12</v>
       </c>
       <c r="G52">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H52">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2043,25 +2046,25 @@
         <v>59</v>
       </c>
       <c r="B53">
-        <v>1537</v>
+        <v>1627</v>
       </c>
       <c r="C53">
-        <v>81.5</v>
+        <v>85.7</v>
       </c>
       <c r="D53">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E53">
-        <v>33.3</v>
+        <v>44.8</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G53">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2069,25 +2072,25 @@
         <v>60</v>
       </c>
       <c r="B54">
-        <v>1664</v>
+        <v>1537</v>
       </c>
       <c r="C54">
-        <v>90.5</v>
+        <v>81.5</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E54">
-        <v>45</v>
+        <v>33.3</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H54">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2095,25 +2098,25 @@
         <v>61</v>
       </c>
       <c r="B55">
-        <v>805</v>
+        <v>1664</v>
       </c>
       <c r="C55">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="D55">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="F55">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G55">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2121,25 +2124,25 @@
         <v>62</v>
       </c>
       <c r="B56">
-        <v>1004</v>
+        <v>805</v>
       </c>
       <c r="C56">
-        <v>82.3</v>
+        <v>90.2</v>
       </c>
       <c r="D56">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="E56">
+        <v>57.1</v>
+      </c>
+      <c r="F56">
+        <v>7</v>
+      </c>
+      <c r="G56">
         <v>12</v>
       </c>
-      <c r="F56">
-        <v>14</v>
-      </c>
-      <c r="G56">
-        <v>10</v>
-      </c>
       <c r="H56">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2147,25 +2150,25 @@
         <v>63</v>
       </c>
       <c r="B57">
-        <v>1803</v>
+        <v>1004</v>
       </c>
       <c r="C57">
-        <v>87.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D57">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E57">
-        <v>48.6</v>
+        <v>12</v>
       </c>
       <c r="F57">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G57">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H57">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2173,25 +2176,25 @@
         <v>64</v>
       </c>
       <c r="B58">
-        <v>1471</v>
+        <v>1803</v>
       </c>
       <c r="C58">
-        <v>71.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D58">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E58">
-        <v>29.4</v>
+        <v>48.6</v>
       </c>
       <c r="F58">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G58">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2199,25 +2202,25 @@
         <v>65</v>
       </c>
       <c r="B59">
-        <v>1248</v>
+        <v>1471</v>
       </c>
       <c r="C59">
-        <v>90.7</v>
+        <v>71.8</v>
       </c>
       <c r="D59">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E59">
-        <v>40</v>
+        <v>29.4</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G59">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2225,25 +2228,25 @@
         <v>66</v>
       </c>
       <c r="B60">
-        <v>1757</v>
+        <v>1248</v>
       </c>
       <c r="C60">
-        <v>84.2</v>
+        <v>90.7</v>
       </c>
       <c r="D60">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="E60">
-        <v>51.2</v>
+        <v>40</v>
       </c>
       <c r="F60">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H60">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2251,25 +2254,25 @@
         <v>67</v>
       </c>
       <c r="B61">
-        <v>987</v>
+        <v>1757</v>
       </c>
       <c r="C61">
-        <v>82.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D61">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E61">
-        <v>28.6</v>
+        <v>51.2</v>
       </c>
       <c r="F61">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G61">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H61">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2277,25 +2280,25 @@
         <v>68</v>
       </c>
       <c r="B62">
-        <v>1483</v>
+        <v>987</v>
       </c>
       <c r="C62">
-        <v>83.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D62">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E62">
-        <v>36.2</v>
+        <v>28.6</v>
       </c>
       <c r="F62">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G62">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H62">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2303,25 +2306,25 @@
         <v>69</v>
       </c>
       <c r="B63">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="C63">
-        <v>79</v>
+        <v>83.3</v>
       </c>
       <c r="D63">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E63">
-        <v>48.7</v>
+        <v>36.2</v>
       </c>
       <c r="F63">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G63">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H63">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2329,25 +2332,25 @@
         <v>70</v>
       </c>
       <c r="B64">
-        <v>1317</v>
+        <v>1488</v>
       </c>
       <c r="C64">
-        <v>89.5</v>
+        <v>79</v>
       </c>
       <c r="D64">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E64">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="F64">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G64">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H64">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2355,25 +2358,25 @@
         <v>71</v>
       </c>
       <c r="B65">
-        <v>1436</v>
+        <v>1317</v>
       </c>
       <c r="C65">
-        <v>83.8</v>
+        <v>89.5</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E65">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G65">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H65">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2381,25 +2384,25 @@
         <v>72</v>
       </c>
       <c r="B66">
-        <v>1083</v>
+        <v>1436</v>
       </c>
       <c r="C66">
-        <v>75.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="D66">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="E66">
-        <v>25.9</v>
+        <v>42.9</v>
       </c>
       <c r="F66">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G66">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H66">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2407,25 +2410,25 @@
         <v>73</v>
       </c>
       <c r="B67">
-        <v>1379</v>
+        <v>1083</v>
       </c>
       <c r="C67">
-        <v>93.90000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E67">
-        <v>69.2</v>
+        <v>25.9</v>
       </c>
       <c r="F67">
+        <v>19</v>
+      </c>
+      <c r="G67">
+        <v>10</v>
+      </c>
+      <c r="H67">
         <v>7</v>
-      </c>
-      <c r="G67">
-        <v>26</v>
-      </c>
-      <c r="H67">
-        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2433,25 +2436,25 @@
         <v>74</v>
       </c>
       <c r="B68">
-        <v>839</v>
+        <v>1379</v>
       </c>
       <c r="C68">
-        <v>85.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D68">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="E68">
-        <v>48.9</v>
+        <v>69.2</v>
       </c>
       <c r="F68">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G68">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H68">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2459,25 +2462,25 @@
         <v>75</v>
       </c>
       <c r="B69">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="C69">
-        <v>85.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D69">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E69">
-        <v>40.4</v>
+        <v>48.9</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G69">
         <v>20</v>
       </c>
       <c r="H69">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2485,25 +2488,25 @@
         <v>76</v>
       </c>
       <c r="B70">
-        <v>1352</v>
+        <v>926</v>
       </c>
       <c r="C70">
-        <v>86.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D70">
+        <v>85</v>
+      </c>
+      <c r="E70">
+        <v>40.4</v>
+      </c>
+      <c r="F70">
+        <v>10</v>
+      </c>
+      <c r="G70">
+        <v>20</v>
+      </c>
+      <c r="H70">
         <v>21</v>
-      </c>
-      <c r="E70">
-        <v>56.2</v>
-      </c>
-      <c r="F70">
-        <v>19</v>
-      </c>
-      <c r="G70">
-        <v>17</v>
-      </c>
-      <c r="H70">
-        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2511,25 +2514,25 @@
         <v>77</v>
       </c>
       <c r="B71">
-        <v>1493</v>
+        <v>1352</v>
       </c>
       <c r="C71">
-        <v>78</v>
+        <v>86.2</v>
       </c>
       <c r="D71">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="E71">
-        <v>38</v>
+        <v>56.2</v>
       </c>
       <c r="F71">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G71">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H71">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2537,25 +2540,25 @@
         <v>78</v>
       </c>
       <c r="B72">
-        <v>1328</v>
+        <v>1493</v>
       </c>
       <c r="C72">
-        <v>82.2</v>
+        <v>78</v>
       </c>
       <c r="D72">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="E72">
-        <v>52.2</v>
+        <v>38</v>
       </c>
       <c r="F72">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G72">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H72">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2563,25 +2566,25 @@
         <v>79</v>
       </c>
       <c r="B73">
-        <v>1204</v>
+        <v>1328</v>
       </c>
       <c r="C73">
-        <v>90.5</v>
+        <v>82.2</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="E73">
-        <v>30.8</v>
+        <v>52.2</v>
       </c>
       <c r="F73">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G73">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2589,25 +2592,25 @@
         <v>80</v>
       </c>
       <c r="B74">
-        <v>1391</v>
+        <v>1204</v>
       </c>
       <c r="C74">
-        <v>93.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D74">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E74">
-        <v>66.7</v>
+        <v>30.8</v>
       </c>
       <c r="F74">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G74">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H74">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2615,25 +2618,25 @@
         <v>81</v>
       </c>
       <c r="B75">
-        <v>892</v>
+        <v>1391</v>
       </c>
       <c r="C75">
-        <v>90.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D75">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E75">
         <v>66.7</v>
       </c>
       <c r="F75">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G75">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2641,25 +2644,25 @@
         <v>82</v>
       </c>
       <c r="B76">
-        <v>1391</v>
+        <v>892</v>
       </c>
       <c r="C76">
-        <v>82.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D76">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="E76">
-        <v>47.7</v>
+        <v>66.7</v>
       </c>
       <c r="F76">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G76">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H76">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2667,25 +2670,25 @@
         <v>83</v>
       </c>
       <c r="B77">
-        <v>1048</v>
+        <v>1391</v>
       </c>
       <c r="C77">
-        <v>83.3</v>
+        <v>82.2</v>
       </c>
       <c r="D77">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E77">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="F77">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G77">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H77">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2693,25 +2696,25 @@
         <v>84</v>
       </c>
       <c r="B78">
-        <v>1444</v>
+        <v>1048</v>
       </c>
       <c r="C78">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="D78">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E78">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F78">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G78">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2719,25 +2722,25 @@
         <v>85</v>
       </c>
       <c r="B79">
-        <v>978</v>
+        <v>1444</v>
       </c>
       <c r="C79">
-        <v>76.8</v>
+        <v>85.2</v>
       </c>
       <c r="D79">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E79">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="F79">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G79">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H79">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2745,25 +2748,25 @@
         <v>86</v>
       </c>
       <c r="B80">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="C80">
-        <v>86.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D80">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E80">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F80">
         <v>7</v>
       </c>
       <c r="G80">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H80">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2771,25 +2774,25 @@
         <v>87</v>
       </c>
       <c r="B81">
-        <v>1050</v>
+        <v>984</v>
       </c>
       <c r="C81">
-        <v>83.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D81">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E81">
-        <v>48.4</v>
+        <v>44.4</v>
       </c>
       <c r="F81">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G81">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H81">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2797,25 +2800,25 @@
         <v>88</v>
       </c>
       <c r="B82">
-        <v>1425</v>
+        <v>1050</v>
       </c>
       <c r="C82">
-        <v>86.5</v>
+        <v>83.7</v>
       </c>
       <c r="D82">
+        <v>81</v>
+      </c>
+      <c r="E82">
+        <v>48.4</v>
+      </c>
+      <c r="F82">
+        <v>12</v>
+      </c>
+      <c r="G82">
         <v>19</v>
       </c>
-      <c r="E82">
-        <v>40.9</v>
-      </c>
-      <c r="F82">
+      <c r="H82">
         <v>15</v>
-      </c>
-      <c r="G82">
-        <v>22</v>
-      </c>
-      <c r="H82">
-        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2823,25 +2826,25 @@
         <v>89</v>
       </c>
       <c r="B83">
-        <v>1291</v>
+        <v>1425</v>
       </c>
       <c r="C83">
-        <v>85.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D83">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="E83">
-        <v>37.5</v>
+        <v>40.9</v>
       </c>
       <c r="F83">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G83">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H83">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2849,25 +2852,25 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <v>1112</v>
+        <v>1291</v>
       </c>
       <c r="C84">
-        <v>92.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D84">
+        <v>72</v>
+      </c>
+      <c r="E84">
+        <v>37.5</v>
+      </c>
+      <c r="F84">
         <v>13</v>
       </c>
-      <c r="E84">
-        <v>100</v>
-      </c>
-      <c r="F84">
-        <v>9</v>
-      </c>
       <c r="G84">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H84">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2875,25 +2878,25 @@
         <v>91</v>
       </c>
       <c r="B85">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="C85">
-        <v>92.3</v>
+        <v>92.8</v>
       </c>
       <c r="D85">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E85">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="F85">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G85">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H85">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2901,25 +2904,25 @@
         <v>92</v>
       </c>
       <c r="B86">
-        <v>805</v>
+        <v>1121</v>
       </c>
       <c r="C86">
-        <v>88.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D86">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E86">
-        <v>47.8</v>
+        <v>66.7</v>
       </c>
       <c r="F86">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G86">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H86">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2927,25 +2930,25 @@
         <v>93</v>
       </c>
       <c r="B87">
-        <v>1460</v>
+        <v>805</v>
       </c>
       <c r="C87">
-        <v>85.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D87">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="E87">
-        <v>42.7</v>
+        <v>47.8</v>
       </c>
       <c r="F87">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G87">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H87">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2953,25 +2956,25 @@
         <v>94</v>
       </c>
       <c r="B88">
-        <v>1525</v>
+        <v>1460</v>
       </c>
       <c r="C88">
-        <v>85.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D88">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E88">
-        <v>46.6</v>
+        <v>42.7</v>
       </c>
       <c r="F88">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G88">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H88">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2979,25 +2982,25 @@
         <v>95</v>
       </c>
       <c r="B89">
-        <v>1422</v>
+        <v>1525</v>
       </c>
       <c r="C89">
-        <v>86.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="D89">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="E89">
-        <v>54.3</v>
+        <v>46.6</v>
       </c>
       <c r="F89">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G89">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H89">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3005,25 +3008,25 @@
         <v>96</v>
       </c>
       <c r="B90">
-        <v>1389</v>
+        <v>1422</v>
       </c>
       <c r="C90">
-        <v>74.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D90">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="E90">
-        <v>50</v>
+        <v>54.3</v>
       </c>
       <c r="F90">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G90">
         <v>14</v>
       </c>
       <c r="H90">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3031,25 +3034,25 @@
         <v>97</v>
       </c>
       <c r="B91">
-        <v>833</v>
+        <v>1389</v>
       </c>
       <c r="C91">
-        <v>72.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D91">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E91">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F91">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G91">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H91">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3057,25 +3060,25 @@
         <v>98</v>
       </c>
       <c r="B92">
-        <v>1048</v>
+        <v>833</v>
       </c>
       <c r="C92">
-        <v>84.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="D92">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E92">
-        <v>58.5</v>
+        <v>37.5</v>
       </c>
       <c r="F92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G92">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H92">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3083,25 +3086,25 @@
         <v>99</v>
       </c>
       <c r="B93">
-        <v>1119</v>
+        <v>1048</v>
       </c>
       <c r="C93">
-        <v>76.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D93">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E93">
-        <v>41.7</v>
+        <v>58.5</v>
       </c>
       <c r="F93">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G93">
         <v>20</v>
       </c>
       <c r="H93">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3109,25 +3112,25 @@
         <v>100</v>
       </c>
       <c r="B94">
-        <v>1170</v>
+        <v>1119</v>
       </c>
       <c r="C94">
-        <v>70.7</v>
+        <v>76.3</v>
       </c>
       <c r="D94">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E94">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="F94">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G94">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H94">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3135,22 +3138,22 @@
         <v>101</v>
       </c>
       <c r="B95">
-        <v>1516</v>
+        <v>1170</v>
       </c>
       <c r="C95">
-        <v>88.2</v>
+        <v>70.7</v>
       </c>
       <c r="D95">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="E95">
-        <v>9</v>
+        <v>40.9</v>
       </c>
       <c r="F95">
         <v>9</v>
       </c>
       <c r="G95">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H95">
         <v>9</v>
@@ -3161,25 +3164,25 @@
         <v>102</v>
       </c>
       <c r="B96">
-        <v>1088</v>
+        <v>1516</v>
       </c>
       <c r="C96">
-        <v>75.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D96">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="E96">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F96">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G96">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H96">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3187,24 +3190,50 @@
         <v>103</v>
       </c>
       <c r="B97">
+        <v>1088</v>
+      </c>
+      <c r="C97">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="D97">
+        <v>73</v>
+      </c>
+      <c r="E97">
+        <v>25</v>
+      </c>
+      <c r="F97">
+        <v>18</v>
+      </c>
+      <c r="G97">
+        <v>17</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98">
         <v>1098</v>
       </c>
-      <c r="C97">
+      <c r="C98">
         <v>83.5</v>
       </c>
-      <c r="D97">
+      <c r="D98">
         <v>87</v>
       </c>
-      <c r="E97">
+      <c r="E98">
         <v>55.8</v>
       </c>
-      <c r="F97">
+      <c r="F98">
         <v>27</v>
       </c>
-      <c r="G97">
+      <c r="G98">
         <v>22</v>
       </c>
-      <c r="H97">
+      <c r="H98">
         <v>53</v>
       </c>
     </row>
